--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/RHODE_ISLAND_2021.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/RHODE_ISLAND_2021.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -457,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -545,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -589,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -604,7 +649,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -620,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -633,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -646,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -659,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -752,7 +847,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -768,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C29">
@@ -781,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C30">
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -807,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Jiquipilco</t>
@@ -820,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -833,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -846,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -859,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -890,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C38">
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>León</t>
@@ -916,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -929,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -949,7 +1104,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C42">
@@ -960,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Acatepec</t>
@@ -973,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -986,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -999,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C46">
@@ -1012,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -1025,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -1038,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C49">
@@ -1051,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C50">
@@ -1064,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C51">
@@ -1077,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -1090,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -1103,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -1116,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -1129,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C56">
@@ -1142,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C57">
@@ -1155,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1186,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Alfajayucan</t>
@@ -1199,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Atotonilco de Tula</t>
+          <t>Atotonilco De Tula</t>
         </is>
       </c>
       <c r="C61">
@@ -1212,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Cardonal</t>
@@ -1225,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Chapantongo</t>
@@ -1238,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -1251,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -1264,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -1277,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nopala de Villagrán</t>
+          <t>Nopala De Villagrán</t>
         </is>
       </c>
       <c r="C67">
@@ -1290,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Tepeapulco</t>
@@ -1303,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerrero</t>
+          <t>Tepehuacán De Guerrero</t>
         </is>
       </c>
       <c r="C69">
@@ -1316,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Tlahuelilpan</t>
@@ -1329,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Tlahuiltepa</t>
@@ -1342,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -1355,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1386,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -1399,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -1412,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C77">
@@ -1425,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C78">
@@ -1438,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1451,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1482,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Arteaga</t>
@@ -1495,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -1508,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1521,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Tarímbaro</t>
@@ -1534,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1547,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -1560,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1573,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1604,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -1617,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1648,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1679,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Santa Cruz Itundujia</t>
@@ -1692,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C97">
@@ -1705,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Zapotitlán Lagunas</t>
@@ -1718,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1749,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -1762,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -1775,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -1788,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C104">
@@ -1801,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -1814,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -1827,9 +2267,14 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C107">
@@ -1840,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -1853,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1866,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>San Nicolás de los Ranchos</t>
+          <t>San Nicolás De Los Ranchos</t>
         </is>
       </c>
       <c r="C110">
@@ -1879,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -1892,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>San Salvador Huixcolotla</t>
@@ -1905,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -1918,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -1931,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1951,7 +2436,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C116">
@@ -1962,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1993,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -2006,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2037,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -2050,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2081,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2112,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -2125,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2156,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -2169,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2200,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Atoyac</t>
@@ -2213,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -2226,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -2239,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -2252,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -2265,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C138">
@@ -2278,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -2291,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -2304,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Tantoyuca</t>
@@ -2317,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Texcatepec</t>
@@ -2330,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -2343,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -2356,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Tlaltetela</t>
@@ -2369,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -2382,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -2395,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2426,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2449,41 +3069,6 @@
       </c>
       <c r="D151">
         <v>1</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 701,861</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Mayo de 2022</t>
-        </is>
       </c>
     </row>
   </sheetData>
